--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -707,7 +707,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
@@ -727,9 +727,6 @@
   </si>
   <si>
     <t>Observation.methodCode</t>
-  </si>
-  <si>
-    <t>non utilisé </t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ObservationMethod|3.0.0</t>
@@ -6374,7 +6371,7 @@
         <v>218</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>228</v>
@@ -6408,7 +6405,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -6446,10 +6443,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6475,10 +6472,10 @@
         <v>162</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6529,7 +6526,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6549,10 +6546,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6650,10 +6647,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6753,10 +6750,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6856,10 +6853,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6959,10 +6956,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7062,10 +7059,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7165,10 +7162,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7266,10 +7263,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7367,10 +7364,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7470,10 +7467,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7501,10 +7498,10 @@
         <v>200</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7575,10 +7572,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7676,39 +7673,39 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E63" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K63" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="F63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7759,7 +7756,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -7779,10 +7776,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7807,11 +7804,11 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7862,7 +7859,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -7882,10 +7879,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7983,10 +7980,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8027,7 +8024,7 @@
         <v>75</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>75</v>
@@ -8086,10 +8083,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8130,7 +8127,7 @@
         <v>75</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>75</v>
@@ -8189,10 +8186,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8233,7 +8230,7 @@
         <v>75</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>75</v>
@@ -8292,10 +8289,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8395,10 +8392,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8439,7 +8436,7 @@
         <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>75</v>
@@ -8498,10 +8495,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8599,10 +8596,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8700,10 +8697,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8803,10 +8800,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8906,10 +8903,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9009,10 +9006,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9040,10 +9037,10 @@
         <v>162</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9074,25 +9071,25 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9112,10 +9109,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9215,10 +9212,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9241,7 +9238,7 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9294,7 +9291,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9314,10 +9311,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9340,7 +9337,7 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9393,7 +9390,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9413,10 +9410,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9439,7 +9436,7 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9492,7 +9489,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9512,10 +9509,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9538,7 +9535,7 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9591,7 +9588,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -9611,10 +9608,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9637,7 +9634,7 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9690,7 +9687,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -9710,10 +9707,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9736,7 +9733,7 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9789,7 +9786,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -9809,10 +9806,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9835,7 +9832,7 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9888,7 +9885,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -9908,10 +9905,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9934,7 +9931,7 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -9987,7 +9984,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10007,10 +10004,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10033,7 +10030,7 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10086,7 +10083,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10106,10 +10103,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10132,7 +10129,7 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10185,7 +10182,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -10205,10 +10202,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10231,11 +10228,11 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10286,7 +10283,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10306,10 +10303,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10407,10 +10404,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10508,10 +10505,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10609,10 +10606,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10710,10 +10707,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10813,10 +10810,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10916,10 +10913,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11019,10 +11016,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11122,10 +11119,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11223,10 +11220,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11260,7 +11257,7 @@
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>75</v>
@@ -11282,7 +11279,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>75</v>
@@ -11300,7 +11297,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11320,10 +11317,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11346,7 +11343,7 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11399,7 +11396,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -11419,10 +11416,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11445,7 +11442,7 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11498,7 +11495,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
